--- a/artfynd/A 12403-2025 artfynd.xlsx
+++ b/artfynd/A 12403-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081602</v>
+        <v>124076705</v>
       </c>
       <c r="B2" t="n">
         <v>57491</v>
@@ -717,20 +717,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandnäsudden öst 2, Pi lm</t>
+          <t>Sandnäsudden öst, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620044</v>
+        <v>620045</v>
       </c>
       <c r="R2" t="n">
-        <v>7293332</v>
+        <v>7293346</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Till synes äldre spår efter tretåig hackspett på björk.</t>
+          <t>Spår av svårbedömd ålder efter tretåig hackspett på björkstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076705</v>
+        <v>124081602</v>
       </c>
       <c r="B3" t="n">
         <v>57491</v>
@@ -836,20 +836,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandnäsudden öst, Pi lm</t>
+          <t>Sandnäsudden öst 2, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620045</v>
+        <v>620044</v>
       </c>
       <c r="R3" t="n">
-        <v>7293346</v>
+        <v>7293332</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spår av svårbedömd ålder efter tretåig hackspett på björkstam.</t>
+          <t>Till synes äldre spår efter tretåig hackspett på björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 12403-2025 artfynd.xlsx
+++ b/artfynd/A 12403-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081602</v>
+        <v>124076705</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -717,20 +717,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandnäsudden öst 2, Pi lm</t>
+          <t>Sandnäsudden öst, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620044</v>
+        <v>620045</v>
       </c>
       <c r="R2" t="n">
-        <v>7293332</v>
+        <v>7293346</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Till synes äldre spår efter tretåig hackspett på björk.</t>
+          <t>Spår av svårbedömd ålder efter tretåig hackspett på björkstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076705</v>
+        <v>124081602</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -836,20 +836,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandnäsudden öst, Pi lm</t>
+          <t>Sandnäsudden öst 2, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620045</v>
+        <v>620044</v>
       </c>
       <c r="R3" t="n">
-        <v>7293346</v>
+        <v>7293332</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spår av svårbedömd ålder efter tretåig hackspett på björkstam.</t>
+          <t>Till synes äldre spår efter tretåig hackspett på björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 12403-2025 artfynd.xlsx
+++ b/artfynd/A 12403-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124076705</v>
+        <v>124081602</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -717,20 +717,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandnäsudden öst, Pi lm</t>
+          <t>Sandnäsudden öst 2, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620045</v>
+        <v>620044</v>
       </c>
       <c r="R2" t="n">
-        <v>7293346</v>
+        <v>7293332</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spår av svårbedömd ålder efter tretåig hackspett på björkstam.</t>
+          <t>Till synes äldre spår efter tretåig hackspett på björk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124081602</v>
+        <v>124076705</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -836,20 +836,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandnäsudden öst 2, Pi lm</t>
+          <t>Sandnäsudden öst, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620044</v>
+        <v>620045</v>
       </c>
       <c r="R3" t="n">
-        <v>7293332</v>
+        <v>7293346</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Till synes äldre spår efter tretåig hackspett på björk.</t>
+          <t>Spår av svårbedömd ålder efter tretåig hackspett på björkstam.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 12403-2025 artfynd.xlsx
+++ b/artfynd/A 12403-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081602</v>
+        <v>134456817</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandnäsudden öst 2, Pi lm</t>
+          <t>Sandnäsudden, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620044</v>
+        <v>619820</v>
       </c>
       <c r="R2" t="n">
-        <v>7293332</v>
+        <v>7293190</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Till synes äldre spår efter tretåig hackspett på björk.</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,77 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingela Edholm Forsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingela Edholm Forsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124076705</v>
+        <v>134456816</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandnäsudden öst, Pi lm</t>
+          <t>Sandnäsudden, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620045</v>
+        <v>619816</v>
       </c>
       <c r="R3" t="n">
-        <v>7293346</v>
+        <v>7293198</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av svårbedömd ålder efter tretåig hackspett på björkstam.</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +877,785 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134456818</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sandnäsudden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>619960</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7293113</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134456819</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sandnäsudden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>620049</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7293085</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134456820</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sandnäsudden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>620038</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7293262</v>
+      </c>
+      <c r="S6" t="n">
+        <v>21</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134456821</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sandnäsudden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>620008</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7293308</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124076705</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sandnäsudden öst, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>620045</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7293346</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår av svårbedömd ålder efter tretåig hackspett på björkstam.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Ingela Edholm Forsberg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Ingela Edholm Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124081602</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sandnäsudden öst 2, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>620044</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7293332</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Till synes äldre spår efter tretåig hackspett på björk.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ingela Edholm Forsberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ingela Edholm Forsberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124081676</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sandnäsudden norr vid fastighetsgräns, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>619845</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7293339</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Troligt spår efter tretåig hackspett på gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ingela Edholm Forsberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ingela Edholm Forsberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12403-2025 artfynd.xlsx
+++ b/artfynd/A 12403-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456817</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456816</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456819</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456820</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456821</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124076705</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081602</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,8 +1701,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>